--- a/app/backends/sveltekit/template/expense_report_template.xlsx
+++ b/app/backends/sveltekit/template/expense_report_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C973B4A-1A81-4246-BF06-0D909283144E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD000C6C-A480-4433-9B18-6AAB78A9959D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17220" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>index</t>
   </si>
@@ -57,6 +57,12 @@
   <si>
     <t>Overdraft</t>
   </si>
+  <si>
+    <t>Receipt_Date</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
 </sst>
 </file>
 
@@ -67,10 +73,16 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -215,9 +227,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="27">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -339,6 +369,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -349,13 +386,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -539,31 +569,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AC477CF2-4DB4-474C-9440-4326D06E009C}" name="summary" displayName="summary" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AC477CF2-4DB4-474C-9440-4326D06E009C}" name="summary" displayName="summary" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F2" xr:uid="{AC477CF2-4DB4-474C-9440-4326D06E009C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7FC60243-15E0-42C6-B4C5-45FA83089881}" name="index" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{7A52332C-6B86-4381-9920-5421CF22B103}" name="Date" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{F54E03A1-A923-4B02-8086-7E77A74D2CBF}" name="Expense" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{9EBB46F5-AC7B-453E-AF3C-F50D340798A0}" name="Cost" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{AAC81F2A-5BDA-4AD5-B272-A2BD5C22A527}" name="Used" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{834F4CF5-09D1-4D59-BA54-1E8E6C03D6EC}" name="Balance" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{7FC60243-15E0-42C6-B4C5-45FA83089881}" name="index" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{7A52332C-6B86-4381-9920-5421CF22B103}" name="Date" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{F54E03A1-A923-4B02-8086-7E77A74D2CBF}" name="Expense" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9EBB46F5-AC7B-453E-AF3C-F50D340798A0}" name="Cost" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{AAC81F2A-5BDA-4AD5-B272-A2BD5C22A527}" name="Used" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{834F4CF5-09D1-4D59-BA54-1E8E6C03D6EC}" name="Balance" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26E4F855-F38E-4CB3-8E23-8FE039357DBE}" name="Table24" displayName="Table24" ref="A1:G2" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26E4F855-F38E-4CB3-8E23-8FE039357DBE}" name="Table24" displayName="Table24" ref="A1:G2" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:G2" xr:uid="{26E4F855-F38E-4CB3-8E23-8FE039357DBE}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6ED61C32-B572-4429-B7B5-9A2B8623AD56}" name="index" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{167FF604-2D7A-43FA-9969-150D32248084}" name="Date" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{E5E4743D-42DF-446E-8E89-61C8479F0FC5}" name="Expense" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{40259CCF-7F2B-4F2B-BA05-834DDD1E1B18}" name="Descriptions" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{937A8FA1-83E2-4875-8338-A1D9290208F7}" name="Amount" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{221162F0-0059-4A2E-96D1-4612DD8EB9A0}" name="Balance" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{EC3746F5-106E-4905-8BE2-83E5C025FB0E}" name="Overdraft" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6ED61C32-B572-4429-B7B5-9A2B8623AD56}" name="index" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{167FF604-2D7A-43FA-9969-150D32248084}" name="Date" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{E5E4743D-42DF-446E-8E89-61C8479F0FC5}" name="Expense" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{40259CCF-7F2B-4F2B-BA05-834DDD1E1B18}" name="Descriptions" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{937A8FA1-83E2-4875-8338-A1D9290208F7}" name="Amount" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{221162F0-0059-4A2E-96D1-4612DD8EB9A0}" name="Balance" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{EC3746F5-106E-4905-8BE2-83E5C025FB0E}" name="Overdraft" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E00C6905-1E3C-4DC7-A114-E33E0C922094}" name="Table10" displayName="Table10" ref="H1:H2" insertRow="1" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="H1:H2" xr:uid="{E00C6905-1E3C-4DC7-A114-E33E0C922094}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{B810A978-2EB6-40D9-BCA3-E3BEA6D51A69}" name="Receipt_Date" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DD8C9F16-996A-4C34-A00F-9312EA7951F1}" name="Table11" displayName="Table11" ref="I1:I2" insertRow="1" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="I1:I2" xr:uid="{DD8C9F16-996A-4C34-A00F-9312EA7951F1}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{7DF5B9FA-0146-41AF-873D-270F04664160}" name="Bank" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -940,18 +990,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEBA95F-444A-410E-9E30-9062422D1BEC}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.5546875" style="20" customWidth="1"/>
     <col min="3" max="3" width="17.109375" style="7" customWidth="1"/>
     <col min="4" max="4" width="16.88671875" style="7" customWidth="1"/>
     <col min="5" max="5" width="17.44140625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="10" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="8" max="8" width="20" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,8 +1025,14 @@
       <c r="G1" s="16" t="s">
         <v>8</v>
       </c>
+      <c r="H1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="19"/>
       <c r="C2" s="6"/>
@@ -984,9 +1042,12 @@
       <c r="G2" s="17"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>